--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G419"/>
+  <dimension ref="A1:G422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11725,6 +11725,87 @@
         <v>389.67</v>
       </c>
       <c r="G419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>391.51</v>
+      </c>
+      <c r="C420" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="D420" t="n">
+        <v>387.63</v>
+      </c>
+      <c r="E420" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="F420" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="C421" t="n">
+        <v>380.85</v>
+      </c>
+      <c r="D421" t="n">
+        <v>386.74</v>
+      </c>
+      <c r="E421" t="n">
+        <v>386.54</v>
+      </c>
+      <c r="F421" t="n">
+        <v>388.42</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="C422" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="D422" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="E422" t="n">
+        <v>386.7</v>
+      </c>
+      <c r="F422" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="G422" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11741,7 +11822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16424,6 +16505,36 @@
       </c>
       <c r="B468" t="n">
         <v>-0.89</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>-0.32</v>
       </c>
     </row>
   </sheetData>
@@ -16592,28 +16703,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3271027293608741</v>
+        <v>0.3268763760448603</v>
       </c>
       <c r="J2" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K2" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2462024530035677</v>
+        <v>0.2486673450241861</v>
       </c>
       <c r="M2" t="n">
-        <v>3.493673711769219</v>
+        <v>3.469326086719036</v>
       </c>
       <c r="N2" t="n">
-        <v>19.3843763480776</v>
+        <v>19.2431824427372</v>
       </c>
       <c r="O2" t="n">
-        <v>4.402769168157422</v>
+        <v>4.386705192138765</v>
       </c>
       <c r="P2" t="n">
-        <v>382.9203065410877</v>
+        <v>382.9227145553822</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16670,28 +16781,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1775826129074171</v>
+        <v>0.1741233279665597</v>
       </c>
       <c r="J3" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K3" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1864118810008988</v>
+        <v>0.1817102997067419</v>
       </c>
       <c r="M3" t="n">
-        <v>2.245372787934772</v>
+        <v>2.24593961105744</v>
       </c>
       <c r="N3" t="n">
-        <v>8.286076350833321</v>
+        <v>8.278938578766933</v>
       </c>
       <c r="O3" t="n">
-        <v>2.878554559294182</v>
+        <v>2.877314473387803</v>
       </c>
       <c r="P3" t="n">
-        <v>379.2046512184514</v>
+        <v>379.2409711345102</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16748,28 +16859,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1484697968949104</v>
+        <v>0.1463854139272885</v>
       </c>
       <c r="J4" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K4" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1252643780583754</v>
+        <v>0.1235164171252568</v>
       </c>
       <c r="M4" t="n">
-        <v>2.287561228908982</v>
+        <v>2.283066975131825</v>
       </c>
       <c r="N4" t="n">
-        <v>9.267071057388248</v>
+        <v>9.220360740311</v>
       </c>
       <c r="O4" t="n">
-        <v>3.044186436043011</v>
+        <v>3.036504691303967</v>
       </c>
       <c r="P4" t="n">
-        <v>384.6962275685095</v>
+        <v>384.7181134516273</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16826,28 +16937,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1376710717743413</v>
+        <v>0.1365321176603673</v>
       </c>
       <c r="J5" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K5" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09912336304986225</v>
+        <v>0.09886930792678128</v>
       </c>
       <c r="M5" t="n">
-        <v>2.324787725210362</v>
+        <v>2.314214690454733</v>
       </c>
       <c r="N5" t="n">
-        <v>10.37030956479954</v>
+        <v>10.30218021270752</v>
       </c>
       <c r="O5" t="n">
-        <v>3.220296502622008</v>
+        <v>3.209700953781756</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9272459362933</v>
+        <v>383.9392043822499</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16904,28 +17015,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05742917785086108</v>
+        <v>0.06021131116087171</v>
       </c>
       <c r="J6" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K6" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02354331332132276</v>
+        <v>0.02608388069661183</v>
       </c>
       <c r="M6" t="n">
-        <v>2.190476086245657</v>
+        <v>2.187533002789694</v>
       </c>
       <c r="N6" t="n">
-        <v>8.108388543461034</v>
+        <v>8.082215723102662</v>
       </c>
       <c r="O6" t="n">
-        <v>2.847523229661355</v>
+        <v>2.84292379832852</v>
       </c>
       <c r="P6" t="n">
-        <v>384.8712151363484</v>
+        <v>384.8416670202234</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16963,7 +17074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G419"/>
+  <dimension ref="A1:G422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32421,6 +32532,117 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>-36.78565913744011,175.09786617614105</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>-36.78562304779181,175.09871915506432</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>-36.78538265118041,175.09953844965239</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>-36.785138423117374,175.10036426673213</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>-36.784854499525,175.10118530726592</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>-36.78565940266229,175.09786624113934</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>-36.785632836901456,175.09872220675734</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>-36.78539022296006,175.09954173501248</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>-36.78514259039511,175.10036639579045</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>-36.784856157432394,175.1011861856301</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>-36.78565701566265,175.09786565615474</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>-36.785630477026814,175.09872147108126</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>-36.78538894681744,175.09954118130005</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>-36.785141256866254,175.10036571449174</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>-36.78485458242037,175.10118535118414</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0172/nzd0172.xlsx
+++ b/data/nzd0172/nzd0172.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G422"/>
+  <dimension ref="A1:G424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11806,6 +11806,60 @@
         <v>388.61</v>
       </c>
       <c r="G422" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>391.75</v>
+      </c>
+      <c r="C423" t="n">
+        <v>381.87</v>
+      </c>
+      <c r="D423" t="n">
+        <v>387.53</v>
+      </c>
+      <c r="E423" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="F423" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>392.46</v>
+      </c>
+      <c r="C424" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="D424" t="n">
+        <v>387.19</v>
+      </c>
+      <c r="E424" t="n">
+        <v>386.83</v>
+      </c>
+      <c r="F424" t="n">
+        <v>388.53</v>
+      </c>
+      <c r="G424" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11822,7 +11876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B471"/>
+  <dimension ref="A1:B473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16535,6 +16589,26 @@
       </c>
       <c r="B471" t="n">
         <v>-0.32</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>0.37</v>
       </c>
     </row>
   </sheetData>
@@ -16703,28 +16777,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3268763760448603</v>
+        <v>0.3271693857232671</v>
       </c>
       <c r="J2" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2486673450241861</v>
+        <v>0.2507993383206488</v>
       </c>
       <c r="M2" t="n">
-        <v>3.469326086719036</v>
+        <v>3.454346953953118</v>
       </c>
       <c r="N2" t="n">
-        <v>19.2431824427372</v>
+        <v>19.15112369029603</v>
       </c>
       <c r="O2" t="n">
-        <v>4.386705192138765</v>
+        <v>4.376199685834277</v>
       </c>
       <c r="P2" t="n">
-        <v>382.9227145553822</v>
+        <v>382.919583161096</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16781,28 +16855,28 @@
         <v>0.0755</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1741233279665597</v>
+        <v>0.1722541314899521</v>
       </c>
       <c r="J3" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K3" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1817102997067419</v>
+        <v>0.179510351920094</v>
       </c>
       <c r="M3" t="n">
-        <v>2.24593961105744</v>
+        <v>2.244445051190854</v>
       </c>
       <c r="N3" t="n">
-        <v>8.278938578766933</v>
+        <v>8.262277397886384</v>
       </c>
       <c r="O3" t="n">
-        <v>2.877314473387803</v>
+        <v>2.874417749368798</v>
       </c>
       <c r="P3" t="n">
-        <v>379.2409711345102</v>
+        <v>379.2606590660317</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16859,28 +16933,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1463854139272885</v>
+        <v>0.1452617902289772</v>
       </c>
       <c r="J4" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K4" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1235164171252568</v>
+        <v>0.1227752727545931</v>
       </c>
       <c r="M4" t="n">
-        <v>2.283066975131825</v>
+        <v>2.278586301681813</v>
       </c>
       <c r="N4" t="n">
-        <v>9.220360740311</v>
+        <v>9.185009537720354</v>
       </c>
       <c r="O4" t="n">
-        <v>3.036504691303967</v>
+        <v>3.030678065667872</v>
       </c>
       <c r="P4" t="n">
-        <v>384.7181134516273</v>
+        <v>384.7299488991265</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16937,28 +17011,28 @@
         <v>0.1019</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1365321176603673</v>
+        <v>0.1359987141080834</v>
       </c>
       <c r="J5" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K5" t="n">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09886930792678128</v>
+        <v>0.09899613975080157</v>
       </c>
       <c r="M5" t="n">
-        <v>2.314214690454733</v>
+        <v>2.306047372277484</v>
       </c>
       <c r="N5" t="n">
-        <v>10.30218021270752</v>
+        <v>10.25545339896167</v>
       </c>
       <c r="O5" t="n">
-        <v>3.209700953781756</v>
+        <v>3.202413683296034</v>
       </c>
       <c r="P5" t="n">
-        <v>383.9392043822499</v>
+        <v>383.9448233484186</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17015,28 +17089,28 @@
         <v>0.1629</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06021131116087171</v>
+        <v>0.06212220971042621</v>
       </c>
       <c r="J6" t="n">
+        <v>423</v>
+      </c>
+      <c r="K6" t="n">
         <v>421</v>
       </c>
-      <c r="K6" t="n">
-        <v>419</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02608388069661183</v>
+        <v>0.02789872607415511</v>
       </c>
       <c r="M6" t="n">
-        <v>2.187533002789694</v>
+        <v>2.185787810195261</v>
       </c>
       <c r="N6" t="n">
-        <v>8.082215723102662</v>
+        <v>8.066881811040343</v>
       </c>
       <c r="O6" t="n">
-        <v>2.84292379832852</v>
+        <v>2.840225661992431</v>
       </c>
       <c r="P6" t="n">
-        <v>384.8416670202234</v>
+        <v>384.8213065631103</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17074,7 +17148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G422"/>
+  <dimension ref="A1:G424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32643,6 +32717,80 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>-36.78565701566265,175.09786565615474</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>-36.78562392181946,175.09871942753688</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>-36.78538350194219,175.09953881879397</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>-36.78513717293404,175.10036362801466</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>-36.78485267582684,175.1011843410654</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>-36.78565073873765,175.09786411786212</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>-36.78562584468029,175.09872002697654</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>-36.785386394532175,175.0995400738753</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>-36.785140173374025,175.1003651609366</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>-36.78485524558332,175.1011857025298</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
